--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,11 +507,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user2</t>
+          <t>123</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -526,32 +526,57 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-04-25 13:04:01</t>
+          <t>2026-04-25 15:03:29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>user3</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>普通用户</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-04-25 15:47:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>普通用户</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-04-25 13:04:12</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-04-25 15:47:52</t>
         </is>
       </c>
     </row>
